--- a/2023/day05/docs/results.xlsx
+++ b/2023/day05/docs/results.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\ricclu\personal\adventofcode\2023\day05\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B818528-0A14-4495-A74E-B46C7383BDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364989E9-990F-4909-9C40-0BFEA008CC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12645" xr2:uid="{36B324BF-345D-4C18-9AEE-1C3C75EFBCA7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{36B324BF-345D-4C18-9AEE-1C3C75EFBCA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="46">
   <si>
     <t>Language</t>
   </si>
@@ -162,6 +163,21 @@
   </si>
   <si>
     <t>Single Process</t>
+  </si>
+  <si>
+    <t>28 cores, evenly sized ranges, inlined</t>
+  </si>
+  <si>
+    <t>Initial design (very bad)</t>
+  </si>
+  <si>
+    <t>10 cores, no range changes, inlined</t>
+  </si>
+  <si>
+    <t>Not inlined (small optimisation)</t>
+  </si>
+  <si>
+    <t>Inlined (fully inlined)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64E1DDA-1A16-4BB9-8C84-931FD2B4E518}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -617,22 +633,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1.1614583333333334E-4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -646,13 +653,16 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
-        <v>1.9441898148148148E-3</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.3311342592592594E-4</v>
+        <v>1.1614583333333334E-4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -663,30 +673,33 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
       </c>
       <c r="E6" s="1">
-        <v>1.1878958333333335E-2</v>
+        <v>1.9441898148148148E-3</v>
       </c>
       <c r="F6" s="1">
-        <v>1.0787384259259259E-3</v>
+        <v>3.3311342592592594E-4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="E7" s="1">
-        <v>4.9768518518518518E-7</v>
+        <v>1.1878958333333335E-2</v>
       </c>
       <c r="F7" s="1">
-        <v>4.7453703703703706E-7</v>
+        <v>1.0787384259259259E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -694,33 +707,33 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="1">
-        <v>2.9636724537037036E-2</v>
+        <v>4.9768518518518518E-7</v>
       </c>
       <c r="F8" s="1">
-        <v>2.6479513888888889E-3</v>
+        <v>4.7453703703703706E-7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
       </c>
       <c r="E9" s="1">
-        <v>9.2592592592592591E-8</v>
+        <v>2.9636724537037036E-2</v>
       </c>
       <c r="F9" s="1">
-        <v>9.2592592592592591E-8</v>
+        <v>2.6479513888888889E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -731,16 +744,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
-        <v>2.8935185185185185E-7</v>
+        <v>9.2592592592592591E-8</v>
       </c>
       <c r="F10" s="1">
-        <v>3.0092592592592594E-7</v>
+        <v>9.2592592592592591E-8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -748,7 +758,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -757,10 +767,10 @@
         <v>21</v>
       </c>
       <c r="E11" s="1">
-        <v>4.3253125000000002E-3</v>
+        <v>2.8935185185185185E-7</v>
       </c>
       <c r="F11" s="1">
-        <v>4.3668981481481477E-4</v>
+        <v>3.0092592592592594E-7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -771,19 +781,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1">
-        <v>1.6129467592592591E-2</v>
+        <v>4.3253125000000002E-3</v>
       </c>
       <c r="F12" s="1">
-        <v>1.1828124999999998E-3</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
+        <v>4.3668981481481477E-4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -797,36 +804,39 @@
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1">
-        <v>0.10376589120370371</v>
+        <v>1.6129467592592591E-2</v>
       </c>
       <c r="F13" s="1">
-        <v>1.9632407407407407E-3</v>
+        <v>1.1828124999999998E-3</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="1">
-        <v>4.6296296296296295E-8</v>
+        <v>0.10376589120370371</v>
       </c>
       <c r="F14" s="1">
-        <v>2.3148148148148148E-8</v>
+        <v>1.9632407407407407E-3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -837,19 +847,16 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1">
-        <v>2.1168981481481481E-5</v>
+        <v>4.6296296296296295E-8</v>
       </c>
       <c r="F15" s="1">
-        <v>7.164351851851852E-6</v>
-      </c>
-      <c r="G15" t="s">
-        <v>34</v>
+        <v>2.3148148148148148E-8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -857,7 +864,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -866,10 +873,10 @@
         <v>27</v>
       </c>
       <c r="E16" s="1">
-        <v>1.0013888888888888E-4</v>
+        <v>2.1168981481481481E-5</v>
       </c>
       <c r="F16" s="1">
-        <v>1.1420138888888891E-4</v>
+        <v>7.164351851851852E-6</v>
       </c>
       <c r="G16" t="s">
         <v>34</v>
@@ -883,33 +890,39 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1">
-        <v>6.9331365740740742E-3</v>
+        <v>1.0013888888888888E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>6.3159375000000004E-3</v>
+        <v>1.1420138888888891E-4</v>
+      </c>
+      <c r="G17" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
       <c r="E18" s="1">
-        <v>7.5231481481481482E-7</v>
+        <v>6.9331365740740742E-3</v>
       </c>
       <c r="F18" s="1">
-        <v>9.1435185185185185E-7</v>
+        <v>6.3159375000000004E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -917,39 +930,39 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
       <c r="E19" s="1">
-        <v>9.7220717592592584E-3</v>
+        <v>7.5231481481481482E-7</v>
       </c>
       <c r="F19" s="1">
-        <v>2.8827430555555555E-3</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
+        <v>9.1435185185185185E-7</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>29</v>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9.7220717592592584E-3</v>
       </c>
       <c r="F20" s="1">
-        <v>3.472222222222222E-8</v>
+        <v>2.8827430555555555E-3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -957,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
@@ -966,15 +979,15 @@
         <v>29</v>
       </c>
       <c r="F21" s="1">
-        <v>3.2060416666666669E-3</v>
+        <v>3.472222222222222E-8</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
@@ -983,7 +996,7 @@
         <v>29</v>
       </c>
       <c r="F22" s="1">
-        <v>7.0601851851851846E-7</v>
+        <v>3.2060416666666669E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -991,7 +1004,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
@@ -1000,27 +1013,24 @@
         <v>29</v>
       </c>
       <c r="F23" s="1">
-        <v>5.0670254629629633E-3</v>
+        <v>7.0601851851851846E-7</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F24" s="1">
-        <v>3.1249999999999997E-7</v>
+        <v>5.0670254629629633E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1028,19 +1038,19 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="1">
-        <v>3.2407407407407406E-7</v>
+        <v>3.1249999999999997E-7</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1068,16 +1078,16 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="1">
-        <v>1.238425925925926E-3</v>
+        <v>3.2407407407407406E-7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1088,16 +1098,16 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="1">
-        <v>4.3285648148148146E-3</v>
-      </c>
-      <c r="G28" t="s">
-        <v>37</v>
+        <v>1.238425925925926E-3</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1110,17 +1120,14 @@
       <c r="C29" t="s">
         <v>40</v>
       </c>
-      <c r="D29" t="s">
-        <v>23</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="1">
-        <v>1.0127314814814815E-2</v>
+        <v>4.3285648148148146E-3</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1131,16 +1138,19 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="1">
-        <v>8.4560185185185183E-2</v>
+        <v>1.0127314814814815E-2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1148,102 +1158,99 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="1">
-        <v>0.3130324074074074</v>
+        <v>1.2173553240740742E-2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1.0416666666666665E-7</v>
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F32" s="1">
-        <v>3.472222222222222E-8</v>
+        <v>2.6862152777777776E-2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1.0416666666666665E-7</v>
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="1">
-        <v>3.472222222222222E-8</v>
+        <v>0.52864583333333337</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="1">
-        <v>5.9189814814814814E-5</v>
+        <v>40</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F34" s="1">
-        <v>7.6736111111111111E-6</v>
+        <v>8.5509259259259257E-2</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
         <v>40</v>
       </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="1">
-        <v>3.8194444444444446E-4</v>
+      <c r="E35" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F35" s="1">
-        <v>4.4131944444444439E-5</v>
+        <v>0.28576388888888887</v>
       </c>
       <c r="G35" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1251,19 +1258,16 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E36" s="1">
-        <v>1.8991203703703705E-3</v>
+        <v>1.0416666666666665E-7</v>
       </c>
       <c r="F36" s="1">
-        <v>1.2576388888888888E-4</v>
+        <v>3.472222222222222E-8</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1271,16 +1275,22 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
         <v>40</v>
       </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
       <c r="E37" s="1">
-        <v>1.380787037037037E-2</v>
+        <v>1.0416666666666665E-7</v>
       </c>
       <c r="F37" s="1">
-        <v>1.1710416666666666E-3</v>
+        <v>3.472222222222222E-8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1291,61 +1301,145 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1">
-        <v>1.4513888888888889E-2</v>
+        <v>5.9189814814814814E-5</v>
       </c>
       <c r="F38" s="1">
-        <v>1.1714004629629631E-3</v>
+        <v>7.6736111111111111E-6</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
         <v>40</v>
       </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
       <c r="E39" s="1">
-        <v>8.1018518518518515E-8</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="F39" s="1">
-        <v>6.944444444444444E-8</v>
+        <v>4.4131944444444439E-5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1.8991203703703705E-3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1.2576388888888888E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1.380787037037037E-2</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1.1710416666666666E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1.4513888888888889E-2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1.1714004629629631E-3</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>13</v>
       </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8.1018518518518515E-8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>6.944444444444444E-8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="1">
         <v>0.1786574074074074</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F44" s="1">
         <v>1.2623032407407407E-3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G40" xr:uid="{D64E1DDA-1A16-4BB9-8C84-931FD2B4E518}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G40">
-      <sortCondition ref="A1:A40"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:G44" xr:uid="{D64E1DDA-1A16-4BB9-8C84-931FD2B4E518}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G48">
+    <sortCondition ref="A2:A48"/>
+    <sortCondition ref="B2:B48"/>
+    <sortCondition ref="F2:F48"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -1354,6 +1448,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBE2347-4D6B-4CE5-8494-BC9FE5BB7A82}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4d12be1c-d27c-4ec9-b239-ad171082eb1d}" enabled="1" method="Privileged" siteId="{f0bdc1c9-5148-4f86-ac40-edd976e1814c}" contentBits="2" removed="0"/>
